--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1201,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Boluspor x Manisa FK</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Boluspor</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Manisa FK</t>
-        </is>
-      </c>
+          <t>Levski Sofia x Lok. Plovdiv</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,37 +1232,45 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1280,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BELGIUM 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Club Brugge x Kortrijk</t>
+          <t>Boluspor x Manisa FK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortrijk</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1319,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="L11" t="n">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1350,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1338,22 +1366,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wolves x Port Vale</t>
+          <t>Club Brugge x Kortrijk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Kortrijk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1372,13 +1400,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
         <v>1.24</v>
       </c>
       <c r="L12" t="n">
-        <v>15.15</v>
+        <v>14.29</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -1403,6 +1431,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1417,22 +1447,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FRANCE 3</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse x Villefranche Beaujolais</t>
+          <t>Wolves x Port Vale</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1451,20 +1481,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="L13" t="n">
-        <v>21.28</v>
+        <v>15.15</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1482,6 +1512,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1496,22 +1528,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IRELAND 2</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bray Wanderers x Finn Harps</t>
+          <t>Bourg-en-Bresse x Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1530,20 +1562,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="K14" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="L14" t="n">
-        <v>15.62</v>
+        <v>21.28</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1561,6 +1593,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1575,22 +1609,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>IRELAND 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ammanford AFC x Colwyn Bay</t>
+          <t>Bray Wanderers x Finn Harps</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ammanford AFC</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1609,20 +1643,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="K15" t="n">
         <v>1.29</v>
       </c>
       <c r="L15" t="n">
-        <v>19.23</v>
+        <v>15.62</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1640,6 +1674,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1659,17 +1695,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The New Saints x Haverfordwest County</t>
+          <t>Ammanford AFC x Colwyn Bay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Ammanford AFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1688,20 +1724,20 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="L16" t="n">
-        <v>16.13</v>
+        <v>19.23</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1719,6 +1755,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1728,27 +1766,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Middlesbrough x Wrexham</t>
+          <t>The New Saints x Haverfordwest County</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1767,20 +1805,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="K17" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="L17" t="n">
-        <v>12.2</v>
+        <v>16.13</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1798,6 +1836,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,37 +1847,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IRELAND 1</t>
+          <t>FRANCE 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers x Dundalk</t>
+          <t>Fleury-Merogis x Amiens</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Fleury-Merogis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1846,37 +1886,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14.29</v>
+        <v>6.06</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>5.85</v>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,27 +1936,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IRELAND 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers x Treaty United</t>
+          <t>Middlesbrough x Wrexham</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1925,20 +1975,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="L19" t="n">
-        <v>24.39</v>
+        <v>12.2</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1956,6 +2006,8 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1965,27 +2017,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>IRELAND 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile) x Cobresal</t>
+          <t>Shamrock Rovers x Dundalk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2004,20 +2056,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="L20" t="n">
-        <v>20.41</v>
+        <v>14.29</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2087,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2044,29 +2098,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>IRELAND 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Levski Sofia x Lok. Plovdiv</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>Cobh Ramblers x Treaty United</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2075,13 +2137,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L21" t="n">
-        <v>8.33</v>
+        <v>24.39</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -2093,25 +2155,280 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Operario-PR x Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Operario-PR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>24</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>200</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1x3</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="T21" t="b">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="W22" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Midland x Deportivo Maipu</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Midland</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Deportivo Maipu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>32</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>200</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile) x Cobresal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3x4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4x3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3x4</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4x3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
